--- a/test perspective analysis.xlsx
+++ b/test perspective analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TaiLieu\Testing\v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716388EF-DE2F-4177-9206-7F6F08B2E780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743B20B6-7444-4FC8-A6DC-10282B162480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Password strength checker" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="227">
   <si>
     <t>OK</t>
     <phoneticPr fontId="1"/>
@@ -470,10 +470,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Failing by providing multibyte/unicode characters</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Exceeding the maximum string length</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -624,6 +620,123 @@
   </si>
   <si>
     <t>Effective viewpoint</t>
+  </si>
+  <si>
+    <t>56,44,43</t>
+  </si>
+  <si>
+    <t>27,28</t>
+  </si>
+  <si>
+    <t>53,54</t>
+  </si>
+  <si>
+    <t>1,2,3,4</t>
+  </si>
+  <si>
+    <t>9,10,11</t>
+  </si>
+  <si>
+    <t>14,44,52</t>
+  </si>
+  <si>
+    <t>23,24,25</t>
+  </si>
+  <si>
+    <t>46,47</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>5,6</t>
+  </si>
+  <si>
+    <t>23,22,24</t>
+  </si>
+  <si>
+    <t>6, 7, 42, 43</t>
+  </si>
+  <si>
+    <t>5, 8, 47</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 51</t>
+  </si>
+  <si>
+    <t>9, 10, 11, 12, 13</t>
+  </si>
+  <si>
+    <t>14, 15, 44, 52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20, 21, 33, 50, </t>
+  </si>
+  <si>
+    <t>16, 17, 18, 19, 48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45, 46, 53, </t>
+  </si>
+  <si>
+    <t>22, 39, 40, 41</t>
+  </si>
+  <si>
+    <t>23, 24, 25 26, 27, 49, 55</t>
+  </si>
+  <si>
+    <t>28, 29, 32</t>
+  </si>
+  <si>
+    <t>1…12, 56</t>
+  </si>
+  <si>
+    <t>13…18, 57, 58</t>
+  </si>
+  <si>
+    <t>40…42</t>
+  </si>
+  <si>
+    <t>43…45</t>
+  </si>
+  <si>
+    <t>1, 21,23, 25, 52,56</t>
+  </si>
+  <si>
+    <t>2, 22, 24, 26, 54, 57</t>
+  </si>
+  <si>
+    <t>3, 5, 11, 15, 19</t>
+  </si>
+  <si>
+    <t>4, 6, 12, 16, 20</t>
+  </si>
+  <si>
+    <t>7…10, 17, 18, 45, 58, 59, 60</t>
+  </si>
+  <si>
+    <t>29, 30</t>
+  </si>
+  <si>
+    <t>31, 32</t>
+  </si>
+  <si>
+    <t>48, 49</t>
+  </si>
+  <si>
+    <t>35, 36</t>
+  </si>
+  <si>
+    <t>33, 34</t>
+  </si>
+  <si>
+    <t>37, 38</t>
+  </si>
+  <si>
+    <t>Failing by providing multibyte/unicode characters</t>
   </si>
 </sst>
 </file>
@@ -711,7 +824,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -754,11 +867,49 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1130,13 +1281,13 @@
   <cols>
     <col min="1" max="1" width="37.44140625" customWidth="1"/>
     <col min="2" max="2" width="66.109375" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" customWidth="1"/>
     <col min="10" max="13" width="4.109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1146,25 +1297,25 @@
         <v>134</v>
       </c>
       <c r="B1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" t="s">
         <v>141</v>
-      </c>
-      <c r="C1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H1" t="s">
-        <v>142</v>
       </c>
       <c r="I1" t="s">
         <v>10</v>
@@ -1182,16 +1333,22 @@
         <v>14</v>
       </c>
       <c r="N1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="C2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
       <c r="F2">
         <v>5</v>
       </c>
@@ -1217,11 +1374,17 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>17</v>
       </c>
+      <c r="C3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
       <c r="F3">
         <v>10</v>
       </c>
@@ -1244,11 +1407,17 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>18</v>
       </c>
+      <c r="C4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
       <c r="F4">
         <v>14</v>
       </c>
@@ -1277,11 +1446,17 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>19</v>
       </c>
+      <c r="C5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
       <c r="F5">
         <v>17</v>
       </c>
@@ -1310,11 +1485,17 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>20</v>
       </c>
+      <c r="C6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
       <c r="F6">
         <v>24</v>
       </c>
@@ -1340,11 +1521,17 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>21</v>
       </c>
+      <c r="C7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
       <c r="F7">
         <v>25</v>
       </c>
@@ -1373,11 +1560,17 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>22</v>
       </c>
+      <c r="C8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
       <c r="F8">
         <v>28</v>
       </c>
@@ -1403,11 +1596,17 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>23</v>
       </c>
+      <c r="C9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
       <c r="F9">
         <v>31</v>
       </c>
@@ -1430,11 +1629,17 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>24</v>
       </c>
+      <c r="C10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
       <c r="F10">
         <v>33</v>
       </c>
@@ -1457,11 +1662,17 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>25</v>
       </c>
+      <c r="C11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
       <c r="F11">
         <v>37</v>
       </c>
@@ -1487,11 +1698,17 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>26</v>
       </c>
+      <c r="C12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
       <c r="F12">
         <v>40</v>
       </c>
@@ -1511,7 +1728,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>27</v>
@@ -1544,10 +1761,16 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>28</v>
+      </c>
+      <c r="C14" s="4">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
       </c>
       <c r="F14">
         <v>44</v>
@@ -1582,6 +1805,7 @@
       <c r="B15" s="13" t="s">
         <v>136</v>
       </c>
+      <c r="C15" s="4"/>
       <c r="F15">
         <v>4</v>
       </c>
@@ -1609,6 +1833,12 @@
       <c r="B16" s="13" t="s">
         <v>31</v>
       </c>
+      <c r="C16" s="4">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
       <c r="F16">
         <v>5</v>
       </c>
@@ -1630,6 +1860,12 @@
       <c r="B17" s="13" t="s">
         <v>32</v>
       </c>
+      <c r="C17" s="4">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
       <c r="F17">
         <v>47</v>
       </c>
@@ -1657,8 +1893,14 @@
       <c r="B18" s="13" t="s">
         <v>135</v>
       </c>
+      <c r="C18" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
       <c r="F18" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G18" t="s">
         <v>16</v>
@@ -1687,8 +1929,14 @@
       <c r="B19" s="13" t="s">
         <v>34</v>
       </c>
+      <c r="C19" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
       <c r="F19" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G19" t="s">
         <v>16</v>
@@ -1717,8 +1965,14 @@
       <c r="B20" s="13" t="s">
         <v>35</v>
       </c>
+      <c r="C20" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
       <c r="F20" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G20" t="s">
         <v>16</v>
@@ -1747,8 +2001,14 @@
       <c r="B21" s="13" t="s">
         <v>36</v>
       </c>
+      <c r="C21" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
       <c r="F21" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G21" t="s">
         <v>16</v>
@@ -1777,6 +2037,12 @@
       <c r="B22" s="13" t="s">
         <v>38</v>
       </c>
+      <c r="C22" s="4">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
       <c r="F22">
         <v>1</v>
       </c>
@@ -1807,6 +2073,12 @@
       <c r="B23" s="13" t="s">
         <v>39</v>
       </c>
+      <c r="C23" s="4">
+        <v>37</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
       <c r="F23">
         <v>3</v>
       </c>
@@ -1834,6 +2106,12 @@
       <c r="B24" s="13" t="s">
         <v>40</v>
       </c>
+      <c r="C24" s="4">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
       <c r="F24">
         <v>4</v>
       </c>
@@ -1880,7 +2158,7 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>138</v>
+        <v>226</v>
       </c>
       <c r="I26" t="s">
         <v>16</v>
@@ -1924,6 +2202,12 @@
       <c r="B28" t="s">
         <v>43</v>
       </c>
+      <c r="C28">
+        <v>41</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
       <c r="J28" t="s">
         <v>16</v>
       </c>
@@ -1939,6 +2223,12 @@
       <c r="B29" t="s">
         <v>44</v>
       </c>
+      <c r="C29">
+        <v>52</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
       <c r="F29">
         <v>14</v>
       </c>
@@ -1981,8 +2271,12 @@
       <c r="B31" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3">
         <v>48</v>
@@ -2005,8 +2299,12 @@
       <c r="B32" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="C32" s="3">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3">
         <v>48</v>
@@ -2029,6 +2327,12 @@
       <c r="B33" t="s">
         <v>48</v>
       </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
       <c r="F33">
         <v>8</v>
       </c>
@@ -2050,6 +2354,12 @@
       <c r="B34" t="s">
         <v>49</v>
       </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
       <c r="F34">
         <v>49</v>
       </c>
@@ -2114,14 +2424,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:M15 A17:M37">
-    <cfRule type="expression" dxfId="7" priority="1">
+  <conditionalFormatting sqref="A14:M15 A17:M37 A2:B13 E2:M13">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>$N2=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A16:L16">
-    <cfRule type="expression" dxfId="6" priority="3">
+  <conditionalFormatting sqref="A16:C16 E16:L16">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>$M16=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>$N16=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:D13">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>$N2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2151,25 +2471,25 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" t="s">
         <v>143</v>
       </c>
-      <c r="C1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E1" t="s">
-        <v>144</v>
-      </c>
       <c r="F1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I1" t="s">
         <v>10</v>
@@ -2187,18 +2507,24 @@
         <v>14</v>
       </c>
       <c r="N1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
         <v>88</v>
       </c>
+      <c r="C2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
       <c r="F2" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -2225,13 +2551,19 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
         <v>89</v>
       </c>
+      <c r="C3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -2263,8 +2595,14 @@
       <c r="B4" t="s">
         <v>54</v>
       </c>
+      <c r="C4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
       <c r="F4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G4" t="s">
         <v>16</v>
@@ -2293,8 +2631,14 @@
       <c r="B5" t="s">
         <v>55</v>
       </c>
+      <c r="C5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
       <c r="F5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
@@ -2323,8 +2667,14 @@
       <c r="B6" t="s">
         <v>56</v>
       </c>
+      <c r="C6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G6" t="s">
         <v>16</v>
@@ -2356,8 +2706,14 @@
       <c r="B7" t="s">
         <v>57</v>
       </c>
+      <c r="C7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G7" t="s">
         <v>16</v>
@@ -2386,8 +2742,14 @@
       <c r="B8" t="s">
         <v>59</v>
       </c>
+      <c r="C8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
       <c r="F8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G8" t="s">
         <v>16</v>
@@ -2419,8 +2781,14 @@
       <c r="B9" t="s">
         <v>60</v>
       </c>
+      <c r="C9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
       <c r="F9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G9" t="s">
         <v>16</v>
@@ -2449,6 +2817,12 @@
       <c r="B10" t="s">
         <v>61</v>
       </c>
+      <c r="C10">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
       <c r="F10">
         <v>48</v>
       </c>
@@ -2476,6 +2850,12 @@
       <c r="B11" t="s">
         <v>63</v>
       </c>
+      <c r="C11" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
       <c r="F11">
         <v>1</v>
       </c>
@@ -2509,6 +2889,12 @@
       <c r="B12" t="s">
         <v>64</v>
       </c>
+      <c r="C12" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
       <c r="F12">
         <v>5</v>
       </c>
@@ -2542,8 +2928,14 @@
       <c r="B13" t="s">
         <v>66</v>
       </c>
+      <c r="C13" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
       <c r="F13" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G13" t="s">
         <v>16</v>
@@ -2575,8 +2967,14 @@
       <c r="B14" t="s">
         <v>67</v>
       </c>
+      <c r="C14">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
       <c r="F14" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G14" t="s">
         <v>16</v>
@@ -2605,6 +3003,12 @@
       <c r="B15" t="s">
         <v>68</v>
       </c>
+      <c r="C15">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
       <c r="F15">
         <v>50</v>
       </c>
@@ -2635,6 +3039,12 @@
       <c r="B16" t="s">
         <v>70</v>
       </c>
+      <c r="C16">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
       <c r="F16">
         <v>31</v>
       </c>
@@ -2665,6 +3075,12 @@
       <c r="B17" t="s">
         <v>71</v>
       </c>
+      <c r="C17">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
       <c r="F17">
         <v>30</v>
       </c>
@@ -2692,6 +3108,12 @@
       <c r="B18" t="s">
         <v>73</v>
       </c>
+      <c r="C18">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
       <c r="F18">
         <v>14</v>
       </c>
@@ -2713,6 +3135,12 @@
       <c r="B19" t="s">
         <v>74</v>
       </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
       <c r="F19">
         <v>16</v>
       </c>
@@ -2734,6 +3162,12 @@
       <c r="B20" t="s">
         <v>76</v>
       </c>
+      <c r="C20">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
       <c r="F20">
         <v>29</v>
       </c>
@@ -2758,6 +3192,12 @@
       <c r="B21" t="s">
         <v>77</v>
       </c>
+      <c r="C21">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
       <c r="F21">
         <v>32</v>
       </c>
@@ -2806,6 +3246,12 @@
       <c r="B23" t="s">
         <v>80</v>
       </c>
+      <c r="C23">
+        <v>49</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
       <c r="F23">
         <v>49</v>
       </c>
@@ -2833,6 +3279,12 @@
       <c r="B24" t="s">
         <v>81</v>
       </c>
+      <c r="C24">
+        <v>53</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
       <c r="I24" t="s">
         <v>0</v>
       </c>
@@ -2854,6 +3306,12 @@
       <c r="B25" t="s">
         <v>82</v>
       </c>
+      <c r="C25">
+        <v>52</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
       <c r="I25" t="s">
         <v>0</v>
       </c>
@@ -2890,6 +3348,12 @@
       <c r="B27" t="s">
         <v>84</v>
       </c>
+      <c r="C27">
+        <v>26</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
       <c r="F27">
         <v>26</v>
       </c>
@@ -2911,8 +3375,11 @@
       <c r="B28" t="s">
         <v>85</v>
       </c>
+      <c r="C28" t="s">
+        <v>182</v>
+      </c>
       <c r="F28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G28" t="s">
         <v>16</v>
@@ -2960,24 +3427,29 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:M3 A9:M30 A5:E7 A8:F8 A4:F4 G4:M8">
-    <cfRule type="expression" dxfId="5" priority="3">
+  <conditionalFormatting sqref="G4:M8 A11:M30 A2:B10 E9:M10 E4:F4 E8:F8 E5:E7 E2:M3">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>$N2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" dxfId="4" priority="8">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>$N5=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$N5=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>$N6=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:D10">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>$N2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2991,12 +3463,12 @@
   <cols>
     <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="4.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -3006,22 +3478,22 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" t="s">
         <v>143</v>
       </c>
-      <c r="C1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E1" t="s">
-        <v>144</v>
-      </c>
       <c r="F1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H1" t="s">
         <v>10</v>
@@ -3039,21 +3511,25 @@
         <v>14</v>
       </c>
       <c r="M1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="28.8">
       <c r="A2" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -3078,18 +3554,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="28.8">
       <c r="A3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>16</v>
@@ -3116,13 +3596,17 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="C4" s="1">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1">
         <v>29</v>
@@ -3152,13 +3636,17 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="1">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1">
         <v>30</v>
@@ -3188,16 +3676,20 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>16</v>
@@ -3224,16 +3716,20 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>16</v>
@@ -3258,18 +3754,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" ht="28.8">
       <c r="A8" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>16</v>
@@ -3293,13 +3793,17 @@
         <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+        <v>139</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>16</v>
@@ -3331,11 +3835,15 @@
       <c r="B10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>16</v>
@@ -3361,8 +3869,12 @@
       <c r="B11" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1">
         <v>33</v>
@@ -3397,11 +3909,15 @@
       <c r="B12" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
@@ -3433,11 +3949,15 @@
       <c r="B13" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>16</v>
@@ -3466,11 +3986,15 @@
       <c r="B14" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>16</v>
@@ -3491,7 +4015,6 @@
         <v>104</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -3510,8 +4033,12 @@
       <c r="B16" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="C16" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D16" t="s">
+        <v>0</v>
+      </c>
       <c r="E16" s="11"/>
       <c r="F16" s="1"/>
       <c r="H16" t="s">
@@ -3541,8 +4068,12 @@
       <c r="B17" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="C17" s="9">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>0</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="9">
         <v>34</v>
@@ -3568,8 +4099,12 @@
       <c r="B18" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="C18" s="9">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>0</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1">
         <v>23</v>
@@ -3602,10 +4137,14 @@
         <v>106</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+        <v>138</v>
+      </c>
+      <c r="C19" s="9">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>0</v>
+      </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1">
         <v>25</v>
@@ -3628,8 +4167,7 @@
       <c r="B20" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="C20" s="9"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="I20" t="s">
@@ -3647,8 +4185,7 @@
       <c r="B21" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="C21" s="9"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="H21" t="s">
@@ -3666,8 +4203,12 @@
       <c r="B22" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="C22" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" t="s">
+        <v>0</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1">
         <v>11</v>
@@ -3693,8 +4234,7 @@
       <c r="B23" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="C23" s="9"/>
       <c r="E23" s="1"/>
       <c r="F23" s="8"/>
       <c r="L23" t="s">
@@ -3712,8 +4252,12 @@
       <c r="B24" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="C24" s="14">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
+        <v>0</v>
+      </c>
       <c r="E24" s="11"/>
       <c r="F24" s="1">
         <v>22</v>
@@ -3745,8 +4289,12 @@
       <c r="B25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="C25" s="9">
+        <v>53</v>
+      </c>
+      <c r="D25" t="s">
+        <v>0</v>
+      </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="H25" t="s">
@@ -3776,8 +4324,12 @@
       <c r="B26" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="C26" s="9">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>0</v>
+      </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1">
         <v>31</v>
@@ -3809,8 +4361,12 @@
       <c r="B27" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>0</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1">
         <v>35</v>
@@ -3845,8 +4401,12 @@
       <c r="B28" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="C28" s="9">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>0</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1">
         <v>37</v>
@@ -3881,11 +4441,15 @@
       <c r="B29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+      <c r="C29" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>16</v>
@@ -3917,11 +4481,15 @@
       <c r="B30" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="C30" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G30" s="1"/>
       <c r="L30" t="s">
@@ -3939,8 +4507,12 @@
       <c r="B31" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="C31" s="1">
+        <v>45</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1">
         <v>48</v>
@@ -3986,8 +4558,12 @@
       <c r="B33" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+      <c r="C33" s="1">
+        <v>23</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1">
         <v>18</v>
@@ -4013,8 +4589,12 @@
       <c r="B34" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="C34" s="1">
+        <v>25</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1">
         <v>25</v>
@@ -4040,8 +4620,12 @@
       <c r="B35" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="C35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -4069,8 +4653,12 @@
       <c r="B36" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="C36" s="1">
+        <v>60</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1">
         <v>48</v>
@@ -4096,8 +4684,12 @@
       <c r="B37" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
+      <c r="C37" s="1">
+        <v>58</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1">
         <v>40</v>
@@ -4123,8 +4715,12 @@
       <c r="B38" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
+      <c r="C38" s="1">
+        <v>59</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1">
         <v>38</v>
@@ -4153,8 +4749,12 @@
       <c r="B39" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+      <c r="C39" s="1">
+        <v>10</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1">
         <v>39</v>
@@ -4186,11 +4786,15 @@
       <c r="B40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
+      <c r="C40" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>16</v>
@@ -4210,8 +4814,12 @@
       <c r="B41" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
+      <c r="C41" s="1">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1">
         <v>44</v>
@@ -4229,14 +4837,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A3:L41">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="A15:L41 A3:B14 E3:L14">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$M2=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:L2">
-    <cfRule type="expression" dxfId="0" priority="4">
+  <conditionalFormatting sqref="A2:B2 E2:L2">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>#REF!=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:D2 D3:D14">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>#REF!=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C14">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$M2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
